--- a/test_input.xlsx
+++ b/test_input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\Projects\Scraping_directory\THE_Email_Scraper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAEB812-C203-4E26-92D0-28125A2A6288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E92132-59E6-43FF-89C0-FAC3B115C10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61857C6C-2429-4F6C-A1A4-3889C722FCF4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Company</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>speedy fuels</t>
-  </si>
-  <si>
-    <t>bluetec haman</t>
   </si>
   <si>
     <t xml:space="preserve">petrol rete </t>
@@ -455,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B466C296-74B3-4969-BF49-4ECFB6711B44}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.42578125" customWidth="1"/>
@@ -485,41 +482,36 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
